--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487638_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487638_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2813</v>
+        <v>7.1807</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1111</v>
+        <v>6.7107</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1702</v>
+        <v>0.47</v>
       </c>
       <c r="G2" t="n">
         <v>4.9365</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.103</v>
+        <v>-0.2036</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0617</v>
+        <v>-0.3387</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1646</v>
+        <v>0.1352</v>
       </c>
       <c r="V2" t="n">
         <v>2.4477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6964</v>
+        <v>3.5874</v>
       </c>
       <c r="E3" t="n">
         <v>1.4016</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2949</v>
+        <v>2.1859</v>
       </c>
       <c r="G3" t="n">
         <v>3.7368</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3266</v>
+        <v>0.2176</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5072</v>
+        <v>0.3982</v>
       </c>
       <c r="V3" t="n">
         <v>3.1257</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3854</v>
+        <v>3.1128</v>
       </c>
       <c r="E4" t="n">
         <v>1.9997</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3856</v>
+        <v>1.1131</v>
       </c>
       <c r="G4" t="n">
         <v>1.9311</v>
@@ -766,13 +766,13 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6662</v>
+        <v>0.3937</v>
       </c>
       <c r="T4" t="n">
         <v>0.0011</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6651</v>
+        <v>0.3926</v>
       </c>
       <c r="V4" t="n">
         <v>1.1761</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5226</v>
+        <v>1.8402</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6716</v>
+        <v>2.071</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1491</v>
+        <v>-0.2308</v>
       </c>
       <c r="G5" t="n">
         <v>1.6771</v>
@@ -844,13 +844,13 @@
         <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9157</v>
+        <v>0.2333</v>
       </c>
       <c r="T5" t="n">
-        <v>0.729</v>
+        <v>0.1284</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1867</v>
+        <v>0.1049</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8462</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2398</v>
+        <v>0.5034</v>
       </c>
       <c r="E6" t="n">
-        <v>0.73</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4902</v>
+        <v>-0.3266</v>
       </c>
       <c r="G6" t="n">
         <v>0.1743</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4002</v>
+        <v>-0.1365</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1579</v>
+        <v>0.0056</v>
       </c>
       <c r="V6" t="n">
         <v>0.6597</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1328</v>
+        <v>0.3147</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1528</v>
+        <v>-0.0527</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2856</v>
+        <v>0.3674</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0428</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2124</v>
+        <v>-0.0306</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2541</v>
+        <v>-0.4454</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4064</v>
+        <v>-0.7067</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1523</v>
+        <v>0.2613</v>
       </c>
       <c r="G8" t="n">
         <v>-0.372</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3519</v>
+        <v>0.1607</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5462</v>
+        <v>0.2459</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1943</v>
+        <v>-0.0852</v>
       </c>
       <c r="V8" t="n">
         <v>0.3481</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9897</v>
+        <v>-1.6805</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.921</v>
+        <v>-2.1212</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9313</v>
+        <v>0.4407</v>
       </c>
       <c r="G9" t="n">
         <v>-0.09320000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>1.26</v>
+        <v>0.5692</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3039</v>
+        <v>0.1037</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.4655</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2161</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9268</v>
+        <v>-2.3718</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3903</v>
+        <v>-4.8898</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4635</v>
+        <v>2.518</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5904</v>
@@ -1234,13 +1234,13 @@
         <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7039</v>
+        <v>-0.1489</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8479</v>
+        <v>-0.3474</v>
       </c>
       <c r="U10" t="n">
-        <v>0.144</v>
+        <v>0.1985</v>
       </c>
       <c r="V10" t="n">
         <v>0.7257</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1986</v>
+        <v>-2.6981</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4071</v>
+        <v>-3.9066</v>
       </c>
       <c r="F11" t="n">
         <v>1.2085</v>
@@ -1312,10 +1312,10 @@
         <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5103</v>
+        <v>-0.0098</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4845</v>
+        <v>0.016</v>
       </c>
       <c r="U11" t="n">
         <v>-0.0258</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.497</v>
+        <v>-4.9514</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8786</v>
+        <v>-5.5783</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3816</v>
+        <v>0.6269</v>
       </c>
       <c r="G12" t="n">
         <v>-1.688</v>
@@ -1390,13 +1390,13 @@
         <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8672</v>
+        <v>-0.3216</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6662</v>
+        <v>-0.3659</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.201</v>
+        <v>0.0443</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1657</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.392099999999999</v>
+        <v>4.391999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.242199999999998</v>
+        <v>-4.2422</v>
       </c>
       <c r="F13" t="n">
-        <v>8.634200000000002</v>
+        <v>8.634399999999999</v>
       </c>
       <c r="G13" t="n">
         <v>7.643499999999999</v>
@@ -1468,10 +1468,10 @@
         <v>13.5823</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7234000000000003</v>
+        <v>0.7234999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7795999999999998</v>
+        <v>-0.7796000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>1.5031</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8756</v>
+        <v>3.2393</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8979</v>
+        <v>3.0981</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0223</v>
+        <v>0.1412</v>
       </c>
       <c r="G14" t="n">
         <v>2.0647</v>
@@ -1546,13 +1546,13 @@
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8847</v>
+        <v>-0.521</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0296</v>
+        <v>-0.8294</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1449</v>
+        <v>0.3084</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2448</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5139</v>
+        <v>2.9143</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9993</v>
+        <v>1.3997</v>
       </c>
       <c r="F15" t="n">
         <v>1.5145</v>
@@ -1624,10 +1624,10 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7156</v>
+        <v>-0.3152</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4845</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>-0.231</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1498</v>
+        <v>0.2504</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6953</v>
+        <v>-1.2949</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8451</v>
+        <v>1.5453</v>
       </c>
       <c r="G16" t="n">
         <v>-4.7312</v>
@@ -1702,13 +1702,13 @@
         <v>2.5224</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6249</v>
+        <v>-0.5243</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9691</v>
+        <v>-0.5687</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3441</v>
+        <v>0.0443</v>
       </c>
       <c r="V16" t="n">
         <v>3.9537</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.116</v>
+        <v>-0.2571</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0609</v>
+        <v>-0.4613</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1768</v>
+        <v>0.2041</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7128</v>
@@ -1780,13 +1780,13 @@
         <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1034</v>
+        <v>-0.2697</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.12</v>
+        <v>-0.5204</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2234</v>
+        <v>0.2507</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2448</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2893</v>
+        <v>-0.3202</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1087</v>
+        <v>-0.4887</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.398</v>
+        <v>0.1685</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6802</v>
+        <v>0.0367</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4988</v>
+        <v>1.2902</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8186</v>
+        <v>-1.2535</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.115</v>
+        <v>1.2167</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4953</v>
+        <v>1.9196</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3803</v>
+        <v>-0.7029</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5652</v>
+        <v>-1.18</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0035</v>
+        <v>-0.6294</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5617</v>
+        <v>-0.5506</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9105</v>
+        <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6745</v>
+        <v>-0.3241</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9118000000000001</v>
+        <v>-0.4055</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2373</v>
+        <v>0.0813</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>-0.8089</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>-0.4791</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5477</v>
+        <v>-0.599</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6889</v>
+        <v>-0.3918</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1413</v>
+        <v>-0.2072</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0367</v>
+        <v>-1.6802</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2902</v>
+        <v>-2.4988</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2535</v>
+        <v>0.8186</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2167</v>
+        <v>-0.115</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9196</v>
+        <v>-1.4953</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7029</v>
+        <v>1.3803</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.18</v>
+        <v>-1.5652</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6294</v>
+        <v>-1.0035</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5506</v>
+        <v>-0.5617</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7463</v>
+        <v>2.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5516</v>
+        <v>0.3648</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6057</v>
+        <v>0.4113</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0541</v>
+        <v>-0.0465</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8089</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4791</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9762</v>
+        <v>-0.9841</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3004</v>
+        <v>-1.7476</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3242</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0464</v>
+        <v>1.6486</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7755</v>
+        <v>1.3355</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8218</v>
+        <v>0.3131</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5619</v>
+        <v>1.0155</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5005</v>
+        <v>1.0916</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9386</v>
+        <v>-0.0762</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6083</v>
+        <v>0.6331</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.725</v>
+        <v>0.2439</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1168</v>
+        <v>0.3893</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7463</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8806</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1344</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1837</v>
+        <v>-0.0028</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8214</v>
+        <v>0.1951</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3623</v>
+        <v>-0.1979</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3672</v>
+        <v>-1.2716</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.803</v>
+        <v>-0.0478</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7031</v>
+        <v>-2.0079</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5484</v>
+        <v>-2.3276</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.3197</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6486</v>
+        <v>-2.7466</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3355</v>
+        <v>-0.5133</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3131</v>
+        <v>-2.2334</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0155</v>
+        <v>-0.5256</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0916</v>
+        <v>0.7456</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0762</v>
+        <v>-1.2712</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6331</v>
+        <v>-2.221</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2439</v>
+        <v>-1.2589</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3893</v>
+        <v>-0.9621</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7218</v>
+        <v>-0.2389</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6057</v>
+        <v>-0.5019</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1162</v>
+        <v>0.263</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2716</v>
+        <v>-0.5746</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0478</v>
+        <v>-0.3299</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-0.2448</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.944</v>
+        <v>-2.3498</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1274</v>
+        <v>-3.4015</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1834</v>
+        <v>1.0517</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7466</v>
+        <v>-0.0464</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5133</v>
+        <v>1.7755</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2334</v>
+        <v>-1.8218</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5256</v>
+        <v>0.5619</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7456</v>
+        <v>2.5005</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2712</v>
+        <v>-1.9386</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.221</v>
+        <v>-0.6083</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2589</v>
+        <v>-0.725</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9621</v>
+        <v>0.1168</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5523</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5224</v>
+        <v>2.1344</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.175</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3017</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1267</v>
+        <v>0.0897</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5746</v>
+        <v>-1.3672</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3299</v>
+        <v>-0.803</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2448</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5872</v>
+        <v>-4.278</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.219</v>
+        <v>-3.0188</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3682</v>
+        <v>-1.2592</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8534</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0115</v>
+        <v>0.2978</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.12</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1086</v>
+        <v>0.2176</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6925</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.392200000000001</v>
+        <v>-4.3921</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.634399999999999</v>
+        <v>-8.634400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>4.2421</v>
+        <v>4.2422</v>
       </c>
       <c r="G24" t="n">
         <v>-7.6434</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4203</v>
+        <v>0.4203000000000005</v>
       </c>
       <c r="I24" t="n">
         <v>-8.063600000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3854</v>
+        <v>4.385399999999999</v>
       </c>
       <c r="K24" t="n">
         <v>6.887699999999999</v>
@@ -2311,7 +2311,7 @@
         <v>-12.0289</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.467399999999999</v>
+        <v>-6.4674</v>
       </c>
       <c r="O24" t="n">
         <v>-5.5612</v>
@@ -2326,22 +2326,22 @@
         <v>22.3138</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7234999999999999</v>
+        <v>-0.7234</v>
       </c>
       <c r="T24" t="n">
         <v>-1.5031</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7796000000000001</v>
+        <v>0.7796</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.756699999999999</v>
+        <v>-4.7567</v>
       </c>
       <c r="W24" t="n">
         <v>2.0655</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.8225</v>
+        <v>-6.822500000000001</v>
       </c>
     </row>
   </sheetData>
